--- a/output/roomself_excel/5714.xlsx
+++ b/output/roomself_excel/5714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33666</v>
+        <v>122861</v>
       </c>
       <c r="D2" t="n">
-        <v>1468</v>
+        <v>3036</v>
       </c>
       <c r="E2" t="n">
-        <v>211</v>
+        <v>523</v>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>118080</v>
+        <v>193400</v>
       </c>
       <c r="D3" t="n">
-        <v>2756</v>
+        <v>3572</v>
       </c>
       <c r="E3" t="n">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="F3" t="n">
-        <v>219</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>413590</v>
+        <v>118080</v>
       </c>
       <c r="D4" t="n">
-        <v>7752</v>
+        <v>2756</v>
       </c>
       <c r="E4" t="n">
-        <v>933</v>
+        <v>320</v>
       </c>
       <c r="F4" t="n">
-        <v>571</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67418</v>
+        <v>155181</v>
       </c>
       <c r="D5" t="n">
-        <v>2356</v>
+        <v>3272</v>
       </c>
       <c r="E5" t="n">
-        <v>374</v>
+        <v>544</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57693</v>
+        <v>67418</v>
       </c>
       <c r="D6" t="n">
-        <v>2724</v>
+        <v>2356</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>155181</v>
+        <v>15375</v>
       </c>
       <c r="D7" t="n">
-        <v>3272</v>
+        <v>992</v>
       </c>
       <c r="E7" t="n">
-        <v>544</v>
+        <v>150</v>
       </c>
       <c r="F7" t="n">
-        <v>335</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14883</v>
+        <v>97329</v>
       </c>
       <c r="D8" t="n">
-        <v>976</v>
+        <v>2540</v>
       </c>
       <c r="E8" t="n">
-        <v>121</v>
+        <v>374</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
@@ -620,20 +620,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15375</v>
+        <v>33666</v>
       </c>
       <c r="D9" t="n">
-        <v>992</v>
+        <v>1468</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="F9" t="n">
-        <v>148</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>57693</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2724</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14883</v>
+      </c>
+      <c r="D11" t="n">
+        <v>976</v>
+      </c>
+      <c r="E11" t="n">
+        <v>121</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5714.xlsx
+++ b/output/roomself_excel/5714.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>3036</v>
       </c>
-      <c r="E2" t="n">
-        <v>523</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>272</v>
+        <v>60</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>438</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>248</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +559,38 @@
       <c r="D3" t="n">
         <v>3572</v>
       </c>
-      <c r="E3" t="n">
-        <v>571</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>397</v>
+        <v>522</v>
+      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>370</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>371</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +608,31 @@
       <c r="D4" t="n">
         <v>2756</v>
       </c>
-      <c r="E4" t="n">
-        <v>320</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>369</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +649,38 @@
       <c r="D5" t="n">
         <v>3272</v>
       </c>
-      <c r="E5" t="n">
-        <v>544</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>335</v>
+        <v>299</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>299</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>519</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +698,31 @@
       <c r="D6" t="n">
         <v>2356</v>
       </c>
-      <c r="E6" t="n">
-        <v>374</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>74</v>
+      </c>
+      <c r="J6" t="n">
         <v>54</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +739,31 @@
       <c r="D7" t="n">
         <v>992</v>
       </c>
-      <c r="E7" t="n">
-        <v>150</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>148</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +780,23 @@
       <c r="D8" t="n">
         <v>2540</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>374</v>
       </c>
-      <c r="F8" t="n">
-        <v>25</v>
-      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +813,31 @@
       <c r="D9" t="n">
         <v>1468</v>
       </c>
-      <c r="E9" t="n">
-        <v>211</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>206</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>181</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +854,23 @@
       <c r="D10" t="n">
         <v>2724</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +887,23 @@
       <c r="D11" t="n">
         <v>976</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>121</v>
       </c>
-      <c r="F11" t="n">
-        <v>25</v>
-      </c>
+      <c r="G11" t="n">
+        <v>25</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
